--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="262">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T13:35:06+00:00</t>
+    <t>2026-08-04T12:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Address|4.0.1</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/Address-eu|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -358,8 +358,8 @@
     <t>Code COG de la ville</t>
   </si>
   <si>
-    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale.
-This extension adds the insee code (5 digits) to the address</t>
+    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale. Dans le cas d'une ville étrangère, le code département devient "99" et le code commune est renseigné avec le code pays. Pour plus de détails, consultez le référentiel national d'identitovigilance (RNIV).
+This extension adds the insee code (5 digits) to the address. In the case of a foreign city, the department code becomes "99", and the municipality code is populated with the country code.</t>
   </si>
   <si>
     <t>Address.use</t>
@@ -372,7 +372,7 @@
 </t>
   </si>
   <si>
-    <t>home | work | temp | old | billing - purpose of this address</t>
+    <t>Purpose of this address</t>
   </si>
   <si>
     <t>The purpose of this address.</t>
@@ -408,7 +408,7 @@
     <t>Address.type</t>
   </si>
   <si>
-    <t>postal | physical | both</t>
+    <t>Address type (postal | physical)</t>
   </si>
   <si>
     <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
@@ -468,6 +468,9 @@
     <t>This component contains the house number, apartment number, street name, street direction,  P.O. Box number, delivery hints, and similar address information.</t>
   </si>
   <si>
+    <t>When extensions are used for providing structured information the line element SHOULD be populated with a human readable representation of the line.</t>
+  </si>
+  <si>
     <t>137 Nowhere Street</t>
   </si>
   <si>
@@ -481,6 +484,87 @@
   </si>
   <si>
     <t>street</t>
+  </si>
+  <si>
+    <t>Address.line.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Address.line.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Address.line.extension:streetName</t>
+  </si>
+  <si>
+    <t>streetName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.3.0}
+</t>
+  </si>
+  <si>
+    <t>streetName.</t>
+  </si>
+  <si>
+    <t>ADXP[partType=STR]</t>
+  </si>
+  <si>
+    <t>Address.line.extension:houseNumber</t>
+  </si>
+  <si>
+    <t>houseNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.3.0}
+</t>
+  </si>
+  <si>
+    <t>The number of a building, house or lot alongside the street. Also known as "primary street number". This does not number the street but rather the building.</t>
+  </si>
+  <si>
+    <t>ADXP[partType=BNR]</t>
+  </si>
+  <si>
+    <t>Address.line.extension:postBox</t>
+  </si>
+  <si>
+    <t>postBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {iso21090-ADXP-postBox|5.3.0}
+</t>
+  </si>
+  <si>
+    <t>A numbered box located in a post station.</t>
+  </si>
+  <si>
+    <t>ADXP[partType=POB]</t>
+  </si>
+  <si>
+    <t>Address.line.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
   </si>
   <si>
     <t>Address.city</t>
@@ -568,7 +652,7 @@
 </t>
   </si>
   <si>
-    <t>Postal code for area</t>
+    <t>Postal code</t>
   </si>
   <si>
     <t>A postal code designating a region defined by the postal service.</t>
@@ -611,6 +695,107 @@
   </si>
   <si>
     <t>country</t>
+  </si>
+  <si>
+    <t>Address.country.id</t>
+  </si>
+  <si>
+    <t>Address.country.extension</t>
+  </si>
+  <si>
+    <t>Address.country.extension:countryCode</t>
+  </si>
+  <si>
+    <t>countryCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {iso21090-codedString|5.3.0}
+</t>
+  </si>
+  <si>
+    <t>code for string</t>
+  </si>
+  <si>
+    <t>Provides a coded expression for the content represented in a string.</t>
+  </si>
+  <si>
+    <t>SC.code</t>
+  </si>
+  <si>
+    <t>Address.country.extension:countryCode.id</t>
+  </si>
+  <si>
+    <t>Address.country.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id
+</t>
+  </si>
+  <si>
+    <t>Address.country.extension:countryCode.extension</t>
+  </si>
+  <si>
+    <t>Address.country.extension.extension</t>
+  </si>
+  <si>
+    <t>Address.country.extension:countryCode.url</t>
+  </si>
+  <si>
+    <t>Address.country.extension.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/iso21090-codedString</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Address.country.extension:countryCode.value[x]</t>
+  </si>
+  <si>
+    <t>Address.country.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2|4.0.1</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>Address.country.value</t>
   </si>
   <si>
     <t>Address.period</t>
@@ -951,12 +1136,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AN29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="24.14453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="16.53515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="40.671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.94921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1953,7 +2138,9 @@
       <c r="M9" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N9" s="2"/>
+      <c r="N9" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>78</v>
@@ -1966,7 +2153,7 @@
         <v>78</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="U9" t="s" s="2">
         <v>78</v>
@@ -2017,28 +2204,28 @@
         <v>86</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2054,7 +2241,7 @@
         <v>78</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>91</v>
@@ -2078,7 +2265,7 @@
         <v>78</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="U10" t="s" s="2">
         <v>78</v>
@@ -2114,7 +2301,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2126,38 +2313,38 @@
         <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>78</v>
@@ -2166,20 +2353,18 @@
         <v>78</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>78</v>
@@ -2192,7 +2377,7 @@
         <v>78</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="U11" t="s" s="2">
         <v>78</v>
@@ -2216,37 +2401,35 @@
         <v>78</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>78</v>
@@ -2257,21 +2440,23 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>78</v>
@@ -2280,16 +2465,16 @@
         <v>78</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2340,50 +2525,52 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
@@ -2392,16 +2579,16 @@
         <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2416,7 +2603,7 @@
         <v>78</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="U13" t="s" s="2">
         <v>78</v>
@@ -2452,41 +2639,43 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>78</v>
       </c>
@@ -2495,7 +2684,7 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
@@ -2504,20 +2693,18 @@
         <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -2566,39 +2753,39 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2618,21 +2805,19 @@
         <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
       </c>
@@ -2644,7 +2829,7 @@
         <v>78</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="U15" t="s" s="2">
         <v>78</v>
@@ -2653,7 +2838,7 @@
         <v>78</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="X15" t="s" s="2">
         <v>78</v>
@@ -2680,7 +2865,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -2692,18 +2877,1592 @@
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AK16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AL18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AC22" s="2"/>
+      <c r="AD22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y27" s="2"/>
+      <c r="Z27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:27:17+00:00</t>
+    <t>2026-08-04T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:47:42+00:00</t>
+    <t>2026-08-07T08:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:01:10+00:00</t>
+    <t>2026-08-07T08:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:58:25+00:00</t>
+    <t>2026-08-07T11:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:57+00:00</t>
+    <t>2026-08-10T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:42:53+00:00</t>
+    <t>2026-08-10T13:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:14:57+00:00</t>
+    <t>2026-08-10T13:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:29:34+00:00</t>
+    <t>2026-08-10T13:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:33:35+00:00</t>
+    <t>2026-08-10T13:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:39:12+00:00</t>
+    <t>2026-08-10T13:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:42:57+00:00</t>
+    <t>2026-08-10T13:45:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:45:29+00:00</t>
+    <t>2026-08-10T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:54:17+00:00</t>
+    <t>2026-08-10T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:12:55+00:00</t>
+    <t>2026-08-10T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:29:18+00:00</t>
+    <t>2026-08-10T16:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:19:09+00:00</t>
+    <t>2026-08-10T16:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:22:30+00:00</t>
+    <t>2026-08-10T16:46:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:46:59+00:00</t>
+    <t>2026-08-11T07:24:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T07:24:13+00:00</t>
+    <t>2026-08-11T10:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:04:20+00:00</t>
+    <t>2026-08-11T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T11:39:02+00:00</t>
+    <t>2026-08-12T13:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:53:29+00:00</t>
+    <t>2026-08-12T14:08:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
